--- a/Clarifications/Clarifications_on_CAR_&_AllCallsData_6OCT.xlsx
+++ b/Clarifications/Clarifications_on_CAR_&_AllCallsData_6OCT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87B0C0CC-F3EA-4532-827B-366B036DC2E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272A8B3F-B4E3-4237-B9D4-145C8801660E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="679" firstSheet="1" activeTab="6" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="679" firstSheet="1" activeTab="1" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -835,51 +835,6 @@
       <rPr>
         <b/>
         <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Question 3: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Scenario 3: What is CBT agent? The customer left after being for 8 minutes on "Front Desk Transfer". Does this mean that the customer were in a queue for front desk and then dropped off? Will this be an example of an abandoned call?
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Answer 3:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="8"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  You will see “CBT” as the answering agent for any Capacity Based Team, which is where we transfer from Webex Contact Center to Webex Calling.  For example, when we blind transfer a call from a WxCC IVR/menu to the front desk, we “queue” the call for a “Front Desk Transfer” queue where the only assigned team is a Capacity Based Team called “Front Desk Transfer”.  Agents sign into Agent Based Teams, but Capacity Based Teams immediately transfer to the DN configured on that CBT.  For the “Front Desk Transfer” team, that configured transfer DN is x6300.  Unfortunately, that’s where WxCC reporting ends and; you’d need to marry it with detailed call history (CDRs) from Webex Calling to determine what ultimately happened with a call transferred outside of WxCC.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
@@ -982,6 +937,96 @@
   </si>
   <si>
     <t>Questions sent by Krish; Answers provided by Mark Grace</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Question 3: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Scenario 3: What is CBT agent? The customer left after being for 8 minutes on "Front Desk Transfer". Does this mean that the customer were in a queue for front desk and then dropped off? Will this be an example of an abandoned call?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Answer 3:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  You will see “CBT” as the answering agent for any Capacity Based Team, which is where we transfer from Webex Contact Center to Webex Calling.  For example, when we blind transfer a call from a WxCC IVR/menu to the front desk, we “queue” the call for a “Front Desk Transfer” queue where the only assigned team is a Capacity Based Team called “Front Desk Transfer”.  Agents sign into Agent Based Teams, but Capacity Based Teams immediately transfer to the DN configured on that CBT.  For the “Front Desk Transfer” team, that configured transfer DN is x6300.  Unfortunately, that’s where WxCC reporting ends and; you’d need to marry it with detailed call history (CDRs) from Webex Calling to determine what ultimately happened with a call transferred outside of WxCC.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Follow-up question: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Thanks for the answer! For the "customer left" scenario, I understand that I can't see CDR, that's ok. However, in the WxCC data, I see that the CBT agent spends 8 minutes to connect the call to DN. Why is it taking 8 minutes? Shouldn't it happen instantaneously? Also, why are there 3 rows of data for CBT agent? The third last and second last rows seem to have the same data recorded in a span of 3 seconds.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Answer</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="8"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: While the transfer happens immediately from the caller’s perspective, the connected duration when we “queue” it to a queue that leverages a Capacity Based Team for a transfer, WxCC has visibility into the continued duration of that call.  That means that as a caller is routing around in Webex Calling (through auto-attendants, leaving voicemails, multiple transfers within Webex Calling, etc.), WxCC will show that connected duration associated with that CBT transfer.
+</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1689,15 +1734,15 @@
   <sheetData>
     <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="Q2" s="9" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="Q3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -1745,9 +1790,9 @@
       <c r="O6" s="12"/>
       <c r="P6" s="12"/>
     </row>
-    <row r="7" spans="1:17" ht="121.8" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:17" ht="244.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="11" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -1863,7 +1908,7 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
@@ -1871,12 +1916,12 @@
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="67.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
@@ -1896,7 +1941,7 @@
     </row>
     <row r="17" spans="1:16" ht="136.19999999999999" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" s="11"/>
       <c r="C17" s="11"/>

--- a/Clarifications/Clarifications_on_CAR_&_AllCallsData_6OCT.xlsx
+++ b/Clarifications/Clarifications_on_CAR_&_AllCallsData_6OCT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akl0407\Desktop\Academia\GitHub\STAT390_LegalAid_Fall2025\Clarifications\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{272A8B3F-B4E3-4237-B9D4-145C8801660E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B87C64B-A745-4305-A9AE-887607E4B1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="679" firstSheet="1" activeTab="1" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="799" firstSheet="1" activeTab="7" xr2:uid="{607C3898-A061-43F2-B8EC-A6C01FB58344}"/>
   </bookViews>
   <sheets>
     <sheet name="termination reason" sheetId="4" state="hidden" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="sys disconnect" sheetId="5" r:id="rId5"/>
     <sheet name="multiple terminations" sheetId="6" r:id="rId6"/>
     <sheet name="Popular numbers (AllCallsData)" sheetId="7" r:id="rId7"/>
+    <sheet name="activity name counts (CAR)" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="850" uniqueCount="321">
   <si>
     <t>Contact Session ID</t>
   </si>
@@ -1027,6 +1028,390 @@
       <t xml:space="preserve">: While the transfer happens immediately from the caller’s perspective, the connected duration when we “queue” it to a queue that leverages a Capacity Based Team for a transfer, WxCC has visibility into the continued duration of that call.  That means that as a caller is routing around in Webex Calling (through auto-attendants, leaving voicemails, multiple transfers within Webex Calling, etc.), WxCC will show that connected duration associated with that CBT transfer.
 </t>
     </r>
+  </si>
+  <si>
+    <t>count</t>
+  </si>
+  <si>
+    <t>ClosedQueueMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalMenu</t>
+  </si>
+  <si>
+    <t>AppointmentMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalOtherMenu</t>
+  </si>
+  <si>
+    <t>FarmworkerMainMenu</t>
+  </si>
+  <si>
+    <t>SuburbanSeniorsMenu</t>
+  </si>
+  <si>
+    <t>BenefitsMenu</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer2</t>
+  </si>
+  <si>
+    <t>ImmigrationMenu</t>
+  </si>
+  <si>
+    <t>EmploymentMenu</t>
+  </si>
+  <si>
+    <t>SubSeniorPreQueueMessage1_1</t>
+  </si>
+  <si>
+    <t>AddressFaxHoursMenu</t>
+  </si>
+  <si>
+    <t>StaffDirectorySpanishTransfer</t>
+  </si>
+  <si>
+    <t>HIVMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalCriminalCaseMenu</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer</t>
+  </si>
+  <si>
+    <t>ChildSupportMenu</t>
+  </si>
+  <si>
+    <t>OtherLegalPersonalInjuryMenu</t>
+  </si>
+  <si>
+    <t>HolidayPrompt</t>
+  </si>
+  <si>
+    <t>GetLoggedInConsumerAgents</t>
+  </si>
+  <si>
+    <t>CollectCallbackNumber</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorOtherAgents</t>
+  </si>
+  <si>
+    <t>ConsumerQueue</t>
+  </si>
+  <si>
+    <t>ComplimentOrComplaintMenu</t>
+  </si>
+  <si>
+    <t>GetLoggedInHousingAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorOtherQueue</t>
+  </si>
+  <si>
+    <t>ImmigrationOtherMenu</t>
+  </si>
+  <si>
+    <t>ConfirmCallbackNumber</t>
+  </si>
+  <si>
+    <t>HousingQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInBenefitsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorTenantAgents</t>
+  </si>
+  <si>
+    <t>ScreenPopProcessComplete</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorBenefitsAgents</t>
+  </si>
+  <si>
+    <t>HIVVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>BenefitsQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorTenantQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorBenefitsQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInEmploymentAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorConsumerAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorFamilyAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorHomeownerAgents</t>
+  </si>
+  <si>
+    <t>FrontDeskTransfer3</t>
+  </si>
+  <si>
+    <t>EmploymentQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorConsumerQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorFamilyQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInADAPTAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorHomeownerQueue</t>
+  </si>
+  <si>
+    <t>TransferToSafeHaven</t>
+  </si>
+  <si>
+    <t>ADAPTQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorADAPTAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInFamilySPAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorADAPTQueue</t>
+  </si>
+  <si>
+    <t>FamilySPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInImmigrationSPAgents</t>
+  </si>
+  <si>
+    <t>WorkersCompMenu</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorEmploymentAgents</t>
+  </si>
+  <si>
+    <t>VeteransBenefitsVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>SubSeniorPreQueueMessage1_2</t>
+  </si>
+  <si>
+    <t>ImmigrationSPQueue</t>
+  </si>
+  <si>
+    <t>DisconnectContact2</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorOtherSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInConsumerSPAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorEmploymentQueue</t>
+  </si>
+  <si>
+    <t>TraffickingVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorBenefitsSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInBenefitsSPAgents</t>
+  </si>
+  <si>
+    <t>ConsumerSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInEducationAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInEmploymentSPAgents</t>
+  </si>
+  <si>
+    <t>BenefitsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorConsumerSPAgents</t>
+  </si>
+  <si>
+    <t>EducationQueue</t>
+  </si>
+  <si>
+    <t>EmploymentSPQueue</t>
+  </si>
+  <si>
+    <t>DisconnectCallbackContact</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorFamilySPAgents</t>
+  </si>
+  <si>
+    <t>MigrantVoicemailTransfer</t>
+  </si>
+  <si>
+    <t>GetLoggedInImmigrationAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorOtherSPQueue</t>
+  </si>
+  <si>
+    <t>ImmigrationQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInOtherSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorConsumerSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorHomeownerSPAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorBenefitsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorEmploymentSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorTenantSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInHousingSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInADAPTSPAgents</t>
+  </si>
+  <si>
+    <t>OtherSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInConsumerSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInBenefitsSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorFamilySPQueue</t>
+  </si>
+  <si>
+    <t>ADAPTSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInFamilySubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInHousingSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInSubSeniorADAPTSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInHomeownerSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>SubSeniorHomeownerSPQueue</t>
+  </si>
+  <si>
+    <t>PlayErrorMessage</t>
+  </si>
+  <si>
+    <t>GetLoggedInEducationSPAgents</t>
+  </si>
+  <si>
+    <t>HousingSPQueue</t>
+  </si>
+  <si>
+    <t>BenefitsSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>ConsumerSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>HousingSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorEmploymentSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInADAPTSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>HomeownerSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorTenantSPQueue</t>
+  </si>
+  <si>
+    <t>EducationSPQueue</t>
+  </si>
+  <si>
+    <t>FamilySubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInBenefitsSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>ADAPTSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>SubSeniorADAPTSPQueue</t>
+  </si>
+  <si>
+    <t>BenefitsSubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInEmploymentSubSeniorsAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInConsumerSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>GetLoggedInOtherSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>OtherSubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInFamilySubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>EmploymentSubSeniorsQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInADAPTSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>ADAPTSubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>ConsumerSubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>FamilySubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInHousingSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>HousingSubSeniorsSPQueue</t>
+  </si>
+  <si>
+    <t>GetLoggedInEmploymentSubSeniorsSPAgents</t>
+  </si>
+  <si>
+    <t>EmploymentSubSeniorsSPQueue</t>
   </si>
 </sst>
 </file>
@@ -6278,4 +6663,1337 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD07D810-8110-4FD1-8A65-1F5B70F5B858}">
+  <dimension ref="A1:B165"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="1" max="1" width="36.89453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="6">
+        <v>267656</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="6">
+        <v>186138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="6">
+        <v>125748</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="6">
+        <v>110890</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6">
+        <v>96331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="6">
+        <v>87903</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B8" s="6">
+        <v>31956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="6">
+        <v>30337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="6">
+        <v>28301</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="6">
+        <v>28035</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="6">
+        <v>27415</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="6">
+        <v>25847</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="6">
+        <v>25721</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="6">
+        <v>24299</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="6">
+        <v>23629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="6">
+        <v>23145</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="6">
+        <v>21736</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="6">
+        <v>20584</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="6">
+        <v>18734</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B21" s="6">
+        <v>17218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+      <c r="B22" s="6">
+        <v>16045</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" s="6">
+        <v>15190</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24" s="6">
+        <v>13946</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>197</v>
+      </c>
+      <c r="B25" s="6">
+        <v>13509</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>79</v>
+      </c>
+      <c r="B26" s="6">
+        <v>12477</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="6">
+        <v>11815</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>70</v>
+      </c>
+      <c r="B28" s="6">
+        <v>11751</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>198</v>
+      </c>
+      <c r="B29" s="6">
+        <v>10243</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="6">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>28</v>
+      </c>
+      <c r="B31" s="6">
+        <v>9390</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="6">
+        <v>9028</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>67</v>
+      </c>
+      <c r="B33" s="6">
+        <v>9028</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="6">
+        <v>8909</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>200</v>
+      </c>
+      <c r="B35" s="6">
+        <v>8030</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="6">
+        <v>7912</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" s="6">
+        <v>7281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>201</v>
+      </c>
+      <c r="B38" s="6">
+        <v>6895</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>202</v>
+      </c>
+      <c r="B39" s="6">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>203</v>
+      </c>
+      <c r="B40" s="6">
+        <v>5272</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>204</v>
+      </c>
+      <c r="B41" s="6">
+        <v>4933</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>89</v>
+      </c>
+      <c r="B42" s="6">
+        <v>4567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" s="6">
+        <v>4025</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>206</v>
+      </c>
+      <c r="B44" s="6">
+        <v>3959</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>207</v>
+      </c>
+      <c r="B45" s="6">
+        <v>3512</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="6">
+        <v>3011</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>93</v>
+      </c>
+      <c r="B47" s="6">
+        <v>2601</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="6">
+        <v>2570</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="6">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>209</v>
+      </c>
+      <c r="B50" s="6">
+        <v>2545</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>210</v>
+      </c>
+      <c r="B51" s="6">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>211</v>
+      </c>
+      <c r="B52" s="6">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>212</v>
+      </c>
+      <c r="B53" s="6">
+        <v>2394</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" s="6">
+        <v>2267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="6">
+        <v>1945</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>213</v>
+      </c>
+      <c r="B56" s="6">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>214</v>
+      </c>
+      <c r="B57" s="6">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>215</v>
+      </c>
+      <c r="B58" s="6">
+        <v>1527</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>216</v>
+      </c>
+      <c r="B59" s="6">
+        <v>1454</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="6">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>217</v>
+      </c>
+      <c r="B61" s="6">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>218</v>
+      </c>
+      <c r="B62" s="6">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>219</v>
+      </c>
+      <c r="B63" s="6">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A64" t="s">
+        <v>220</v>
+      </c>
+      <c r="B64" s="6">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A65" t="s">
+        <v>221</v>
+      </c>
+      <c r="B65" s="6">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A66" t="s">
+        <v>222</v>
+      </c>
+      <c r="B66" s="6">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A67" t="s">
+        <v>223</v>
+      </c>
+      <c r="B67" s="6">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A68" t="s">
+        <v>224</v>
+      </c>
+      <c r="B68" s="6">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A69" t="s">
+        <v>225</v>
+      </c>
+      <c r="B69" s="6">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A70" t="s">
+        <v>226</v>
+      </c>
+      <c r="B70" s="6">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A71" t="s">
+        <v>227</v>
+      </c>
+      <c r="B71" s="6">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A72" t="s">
+        <v>228</v>
+      </c>
+      <c r="B72" s="6">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A73" t="s">
+        <v>229</v>
+      </c>
+      <c r="B73" s="6">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A74" t="s">
+        <v>230</v>
+      </c>
+      <c r="B74" s="6">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A75" t="s">
+        <v>48</v>
+      </c>
+      <c r="B75" s="6">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A76" t="s">
+        <v>231</v>
+      </c>
+      <c r="B76" s="6">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A77" t="s">
+        <v>232</v>
+      </c>
+      <c r="B77" s="6">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A78" t="s">
+        <v>233</v>
+      </c>
+      <c r="B78" s="6">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A79" t="s">
+        <v>234</v>
+      </c>
+      <c r="B79" s="6">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A80" t="s">
+        <v>235</v>
+      </c>
+      <c r="B80" s="6">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A81" t="s">
+        <v>236</v>
+      </c>
+      <c r="B81" s="6">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A82" t="s">
+        <v>237</v>
+      </c>
+      <c r="B82" s="6">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A83" t="s">
+        <v>238</v>
+      </c>
+      <c r="B83" s="6">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A84" t="s">
+        <v>239</v>
+      </c>
+      <c r="B84" s="6">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A85" t="s">
+        <v>240</v>
+      </c>
+      <c r="B85" s="6">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A86" t="s">
+        <v>241</v>
+      </c>
+      <c r="B86" s="6">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A87" t="s">
+        <v>242</v>
+      </c>
+      <c r="B87" s="6">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A88" t="s">
+        <v>243</v>
+      </c>
+      <c r="B88" s="6">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A89" t="s">
+        <v>244</v>
+      </c>
+      <c r="B89" s="6">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A90" t="s">
+        <v>245</v>
+      </c>
+      <c r="B90" s="6">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A91" t="s">
+        <v>246</v>
+      </c>
+      <c r="B91" s="6">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A92" t="s">
+        <v>247</v>
+      </c>
+      <c r="B92" s="6">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A93" t="s">
+        <v>248</v>
+      </c>
+      <c r="B93" s="6">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A94" t="s">
+        <v>249</v>
+      </c>
+      <c r="B94" s="6">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A95" t="s">
+        <v>250</v>
+      </c>
+      <c r="B95" s="6">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A96" t="s">
+        <v>251</v>
+      </c>
+      <c r="B96" s="6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A97" t="s">
+        <v>252</v>
+      </c>
+      <c r="B97" s="6">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A98" t="s">
+        <v>253</v>
+      </c>
+      <c r="B98" s="6">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A99" t="s">
+        <v>254</v>
+      </c>
+      <c r="B99" s="6">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A100" t="s">
+        <v>255</v>
+      </c>
+      <c r="B100" s="6">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A101" t="s">
+        <v>256</v>
+      </c>
+      <c r="B101" s="6">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A102" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" s="6">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A103" t="s">
+        <v>258</v>
+      </c>
+      <c r="B103" s="6">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A104" t="s">
+        <v>259</v>
+      </c>
+      <c r="B104" s="6">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A105" t="s">
+        <v>260</v>
+      </c>
+      <c r="B105" s="6">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A106" t="s">
+        <v>261</v>
+      </c>
+      <c r="B106" s="6">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A107" t="s">
+        <v>262</v>
+      </c>
+      <c r="B107" s="6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A108" t="s">
+        <v>263</v>
+      </c>
+      <c r="B108" s="6">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>264</v>
+      </c>
+      <c r="B109" s="6">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>265</v>
+      </c>
+      <c r="B110" s="6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>266</v>
+      </c>
+      <c r="B111" s="6">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>267</v>
+      </c>
+      <c r="B112" s="6">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>268</v>
+      </c>
+      <c r="B113" s="6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>269</v>
+      </c>
+      <c r="B114" s="6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>270</v>
+      </c>
+      <c r="B115" s="6">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>271</v>
+      </c>
+      <c r="B116" s="6">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>272</v>
+      </c>
+      <c r="B117" s="6">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>273</v>
+      </c>
+      <c r="B118" s="6">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>274</v>
+      </c>
+      <c r="B119" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>275</v>
+      </c>
+      <c r="B120" s="6">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" t="s">
+        <v>276</v>
+      </c>
+      <c r="B121" s="6">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>277</v>
+      </c>
+      <c r="B122" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" t="s">
+        <v>278</v>
+      </c>
+      <c r="B123" s="6">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
+        <v>279</v>
+      </c>
+      <c r="B124" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>280</v>
+      </c>
+      <c r="B125" s="6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" s="6">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" t="s">
+        <v>283</v>
+      </c>
+      <c r="B128" s="6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>284</v>
+      </c>
+      <c r="B129" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" t="s">
+        <v>285</v>
+      </c>
+      <c r="B130" s="6">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" t="s">
+        <v>286</v>
+      </c>
+      <c r="B131" s="6">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>287</v>
+      </c>
+      <c r="B132" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" t="s">
+        <v>288</v>
+      </c>
+      <c r="B133" s="6">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" t="s">
+        <v>289</v>
+      </c>
+      <c r="B134" s="6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" s="6">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" t="s">
+        <v>291</v>
+      </c>
+      <c r="B136" s="6">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" t="s">
+        <v>292</v>
+      </c>
+      <c r="B137" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" t="s">
+        <v>293</v>
+      </c>
+      <c r="B138" s="6">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" t="s">
+        <v>294</v>
+      </c>
+      <c r="B139" s="6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" t="s">
+        <v>295</v>
+      </c>
+      <c r="B140" s="6">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" t="s">
+        <v>296</v>
+      </c>
+      <c r="B141" s="6">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" t="s">
+        <v>297</v>
+      </c>
+      <c r="B142" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" t="s">
+        <v>298</v>
+      </c>
+      <c r="B143" s="6">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" t="s">
+        <v>299</v>
+      </c>
+      <c r="B144" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" t="s">
+        <v>300</v>
+      </c>
+      <c r="B145" s="6">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" t="s">
+        <v>301</v>
+      </c>
+      <c r="B146" s="6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" t="s">
+        <v>302</v>
+      </c>
+      <c r="B147" s="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>303</v>
+      </c>
+      <c r="B148" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" t="s">
+        <v>304</v>
+      </c>
+      <c r="B149" s="6">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" t="s">
+        <v>305</v>
+      </c>
+      <c r="B150" s="6">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" t="s">
+        <v>306</v>
+      </c>
+      <c r="B151" s="6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" t="s">
+        <v>307</v>
+      </c>
+      <c r="B152" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>308</v>
+      </c>
+      <c r="B153" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" t="s">
+        <v>309</v>
+      </c>
+      <c r="B154" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" t="s">
+        <v>310</v>
+      </c>
+      <c r="B155" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" t="s">
+        <v>311</v>
+      </c>
+      <c r="B156" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" t="s">
+        <v>312</v>
+      </c>
+      <c r="B157" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" t="s">
+        <v>313</v>
+      </c>
+      <c r="B158" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" t="s">
+        <v>314</v>
+      </c>
+      <c r="B159" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" t="s">
+        <v>315</v>
+      </c>
+      <c r="B160" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" t="s">
+        <v>316</v>
+      </c>
+      <c r="B161" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" t="s">
+        <v>317</v>
+      </c>
+      <c r="B162" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" t="s">
+        <v>318</v>
+      </c>
+      <c r="B163" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" t="s">
+        <v>319</v>
+      </c>
+      <c r="B164" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" t="s">
+        <v>320</v>
+      </c>
+      <c r="B165" s="6">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>